--- a/data/tabla.xlsx
+++ b/data/tabla.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\Proyectos\juventud-san-rafael\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4490E1BB-117F-4B08-8F5B-980558B38CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC47363C-E91D-417B-95C9-FCFC19116AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,12 +61,6 @@
     <t>Santa Rosa Sur</t>
   </si>
   <si>
-    <t>Senior 35</t>
-  </si>
-  <si>
-    <t>Senior 34</t>
-  </si>
-  <si>
     <t>2026-08-25</t>
   </si>
   <si>
@@ -95,6 +89,12 @@
   </si>
   <si>
     <t>Juventud Nueva Estrella</t>
+  </si>
+  <si>
+    <t>Sr35</t>
+  </si>
+  <si>
+    <t>Sr45</t>
   </si>
 </sst>
 </file>
@@ -486,19 +486,19 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -524,19 +524,19 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -562,19 +562,19 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -600,19 +600,19 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -638,19 +638,19 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -676,19 +676,19 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D7">
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -714,19 +714,19 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D8">
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -752,19 +752,19 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D9">
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -790,19 +790,19 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D10">
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -828,19 +828,19 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -866,19 +866,19 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D12">
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -904,19 +904,19 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -942,19 +942,19 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D14">
         <v>4</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F14">
         <v>0</v>
